--- a/Thesis/data/raw/autoic/coded-Gramsci_Longitudinal.xlsx
+++ b/Thesis/data/raw/autoic/coded-Gramsci_Longitudinal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kathrene.conway\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b4dcdb2932ef22e/Documents/Integrative-Data-Project/Thesis/data/raw/autoic/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_73248C385204CCB08B5044F349244651EA1734F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="190" yWindow="0" windowWidth="19030" windowHeight="8700" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paragraph" sheetId="1" r:id="rId1"/>
@@ -2449,7 +2450,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -2494,11 +2495,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2520,9 +2521,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2560,9 +2561,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2597,7 +2598,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2632,7 +2633,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2805,20 +2806,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N736"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2862,7 +2863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -2994,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -3038,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -3082,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -3126,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -3170,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -3214,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -3258,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -3346,7 +3347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -3434,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -3522,7 +3523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
@@ -3566,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -3610,7 +3611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -3654,7 +3655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>31</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -3742,7 +3743,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -3786,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3830,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -3918,7 +3919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
@@ -3962,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
@@ -4006,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -4094,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -4182,7 +4183,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -4270,7 +4271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -4314,7 +4315,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -4358,7 +4359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
@@ -4402,7 +4403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>33</v>
       </c>
@@ -4446,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -4490,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>33</v>
       </c>
@@ -4534,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4578,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>33</v>
       </c>
@@ -4622,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>33</v>
       </c>
@@ -4666,7 +4667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>34</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
@@ -4754,7 +4755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>34</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>34</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>34</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>34</v>
       </c>
@@ -4930,7 +4931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>34</v>
       </c>
@@ -4974,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>34</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>34</v>
       </c>
@@ -5062,7 +5063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>34</v>
       </c>
@@ -5106,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>34</v>
       </c>
@@ -5150,7 +5151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>34</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>34</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>34</v>
       </c>
@@ -5282,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>34</v>
       </c>
@@ -5326,7 +5327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>34</v>
       </c>
@@ -5414,7 +5415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>34</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>34</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>34</v>
       </c>
@@ -5546,7 +5547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>34</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>34</v>
       </c>
@@ -5634,7 +5635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>34</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>34</v>
       </c>
@@ -5722,7 +5723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>34</v>
       </c>
@@ -5766,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>34</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>34</v>
       </c>
@@ -5854,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>34</v>
       </c>
@@ -5898,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
@@ -5942,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>34</v>
       </c>
@@ -5986,7 +5987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>34</v>
       </c>
@@ -6030,7 +6031,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>34</v>
       </c>
@@ -6074,7 +6075,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>34</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>34</v>
       </c>
@@ -6162,7 +6163,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>34</v>
       </c>
@@ -6206,7 +6207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>34</v>
       </c>
@@ -6250,7 +6251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>34</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>34</v>
       </c>
@@ -6338,7 +6339,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>34</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>34</v>
       </c>
@@ -6426,7 +6427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>34</v>
       </c>
@@ -6470,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>34</v>
       </c>
@@ -6514,7 +6515,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>34</v>
       </c>
@@ -6558,7 +6559,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>34</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>35</v>
       </c>
@@ -6646,7 +6647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>35</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>35</v>
       </c>
@@ -6734,7 +6735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>35</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>35</v>
       </c>
@@ -6822,7 +6823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>35</v>
       </c>
@@ -6866,7 +6867,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>35</v>
       </c>
@@ -6910,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>35</v>
       </c>
@@ -6998,7 +6999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>35</v>
       </c>
@@ -7042,7 +7043,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>35</v>
       </c>
@@ -7086,7 +7087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>35</v>
       </c>
@@ -7130,7 +7131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -7174,7 +7175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>36</v>
       </c>
@@ -7218,7 +7219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>36</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>36</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>36</v>
       </c>
@@ -7350,7 +7351,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>36</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>36</v>
       </c>
@@ -7438,7 +7439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>37</v>
       </c>
@@ -7482,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
@@ -7526,7 +7527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>37</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>37</v>
       </c>
@@ -7614,7 +7615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>37</v>
       </c>
@@ -7658,7 +7659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>37</v>
       </c>
@@ -7702,7 +7703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>37</v>
       </c>
@@ -7746,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>37</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>38</v>
       </c>
@@ -7834,7 +7835,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>38</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>38</v>
       </c>
@@ -7922,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>38</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>38</v>
       </c>
@@ -8010,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>38</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>38</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>38</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>38</v>
       </c>
@@ -8186,7 +8187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>38</v>
       </c>
@@ -8274,7 +8275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>38</v>
       </c>
@@ -8318,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>38</v>
       </c>
@@ -8362,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>38</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>38</v>
       </c>
@@ -8450,7 +8451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>38</v>
       </c>
@@ -8494,7 +8495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>39</v>
       </c>
@@ -8538,7 +8539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>39</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>39</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
@@ -8670,7 +8671,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>39</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>39</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>39</v>
       </c>
@@ -8802,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>39</v>
       </c>
@@ -8846,7 +8847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>39</v>
       </c>
@@ -8890,7 +8891,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>39</v>
       </c>
@@ -8934,7 +8935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>39</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>39</v>
       </c>
@@ -9022,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>39</v>
       </c>
@@ -9066,7 +9067,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>39</v>
       </c>
@@ -9110,7 +9111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>39</v>
       </c>
@@ -9154,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -9198,7 +9199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -9242,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>40</v>
       </c>
@@ -9286,7 +9287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>40</v>
       </c>
@@ -9330,7 +9331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>40</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>40</v>
       </c>
@@ -9418,7 +9419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -9462,7 +9463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>40</v>
       </c>
@@ -9506,7 +9507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>40</v>
       </c>
@@ -9550,7 +9551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>40</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>40</v>
       </c>
@@ -9638,7 +9639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>41</v>
       </c>
@@ -9682,7 +9683,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>41</v>
       </c>
@@ -9726,7 +9727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>41</v>
       </c>
@@ -9770,7 +9771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>41</v>
       </c>
@@ -9814,7 +9815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>41</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>41</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>41</v>
       </c>
@@ -9946,7 +9947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>41</v>
       </c>
@@ -9990,7 +9991,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>41</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>41</v>
       </c>
@@ -10078,7 +10079,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>41</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>41</v>
       </c>
@@ -10166,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>41</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>41</v>
       </c>
@@ -10254,7 +10255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>41</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>41</v>
       </c>
@@ -10342,7 +10343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>42</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>42</v>
       </c>
@@ -10430,7 +10431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>42</v>
       </c>
@@ -10474,7 +10475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>42</v>
       </c>
@@ -10518,7 +10519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>42</v>
       </c>
@@ -10562,7 +10563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>42</v>
       </c>
@@ -10606,7 +10607,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>42</v>
       </c>
@@ -10650,7 +10651,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>42</v>
       </c>
@@ -10694,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>42</v>
       </c>
@@ -10738,7 +10739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>42</v>
       </c>
@@ -10782,7 +10783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>42</v>
       </c>
@@ -10826,7 +10827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>42</v>
       </c>
@@ -10870,7 +10871,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>43</v>
       </c>
@@ -10914,7 +10915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>43</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>43</v>
       </c>
@@ -11002,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>43</v>
       </c>
@@ -11046,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>43</v>
       </c>
@@ -11090,7 +11091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>43</v>
       </c>
@@ -11134,7 +11135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>43</v>
       </c>
@@ -11178,7 +11179,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>43</v>
       </c>
@@ -11222,7 +11223,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="192" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>43</v>
       </c>
@@ -11266,7 +11267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>44</v>
       </c>
@@ -11310,7 +11311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>44</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>44</v>
       </c>
@@ -11398,7 +11399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>44</v>
       </c>
@@ -11442,7 +11443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>44</v>
       </c>
@@ -11486,7 +11487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>44</v>
       </c>
@@ -11530,7 +11531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>44</v>
       </c>
@@ -11574,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>44</v>
       </c>
@@ -11618,7 +11619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>44</v>
       </c>
@@ -11662,7 +11663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>44</v>
       </c>
@@ -11706,7 +11707,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>44</v>
       </c>
@@ -11750,7 +11751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>44</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>44</v>
       </c>
@@ -11838,7 +11839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>45</v>
       </c>
@@ -11882,7 +11883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>45</v>
       </c>
@@ -11926,7 +11927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>45</v>
       </c>
@@ -11970,7 +11971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>45</v>
       </c>
@@ -12014,7 +12015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>45</v>
       </c>
@@ -12058,7 +12059,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>45</v>
       </c>
@@ -12102,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>45</v>
       </c>
@@ -12146,7 +12147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>45</v>
       </c>
@@ -12190,7 +12191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>45</v>
       </c>
@@ -12234,7 +12235,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>45</v>
       </c>
@@ -12278,7 +12279,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>45</v>
       </c>
@@ -12322,7 +12323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>45</v>
       </c>
@@ -12366,7 +12367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>45</v>
       </c>
@@ -12410,7 +12411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>45</v>
       </c>
@@ -12454,7 +12455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>45</v>
       </c>
@@ -12498,7 +12499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>45</v>
       </c>
@@ -12542,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>45</v>
       </c>
@@ -12586,7 +12587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>45</v>
       </c>
@@ -12630,7 +12631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>45</v>
       </c>
@@ -12674,7 +12675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>45</v>
       </c>
@@ -12718,7 +12719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>45</v>
       </c>
@@ -12762,7 +12763,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="227" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>45</v>
       </c>
@@ -12806,7 +12807,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>45</v>
       </c>
@@ -12850,7 +12851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>45</v>
       </c>
@@ -12894,7 +12895,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>45</v>
       </c>
@@ -12938,7 +12939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>45</v>
       </c>
@@ -12982,7 +12983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>45</v>
       </c>
@@ -13026,7 +13027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>45</v>
       </c>
@@ -13070,7 +13071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>45</v>
       </c>
@@ -13114,7 +13115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>45</v>
       </c>
@@ -13158,7 +13159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>45</v>
       </c>
@@ -13202,7 +13203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>45</v>
       </c>
@@ -13246,7 +13247,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>45</v>
       </c>
@@ -13290,7 +13291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>45</v>
       </c>
@@ -13334,7 +13335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>45</v>
       </c>
@@ -13378,7 +13379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>45</v>
       </c>
@@ -13422,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>45</v>
       </c>
@@ -13466,7 +13467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>45</v>
       </c>
@@ -13510,7 +13511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>45</v>
       </c>
@@ -13554,7 +13555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>45</v>
       </c>
@@ -13598,7 +13599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>45</v>
       </c>
@@ -13642,7 +13643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>45</v>
       </c>
@@ -13686,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>45</v>
       </c>
@@ -13730,7 +13731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>45</v>
       </c>
@@ -13774,7 +13775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>45</v>
       </c>
@@ -13818,7 +13819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>45</v>
       </c>
@@ -13862,7 +13863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>46</v>
       </c>
@@ -13906,7 +13907,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>46</v>
       </c>
@@ -13950,7 +13951,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>46</v>
       </c>
@@ -13994,7 +13995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
         <v>46</v>
       </c>
@@ -14038,7 +14039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>46</v>
       </c>
@@ -14082,7 +14083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
         <v>46</v>
       </c>
@@ -14126,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
         <v>46</v>
       </c>
@@ -14170,7 +14171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
         <v>46</v>
       </c>
@@ -14214,7 +14215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>46</v>
       </c>
@@ -14258,7 +14259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
         <v>46</v>
       </c>
@@ -14302,7 +14303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>46</v>
       </c>
@@ -14346,7 +14347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>46</v>
       </c>
@@ -14390,7 +14391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>46</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>47</v>
       </c>
@@ -14478,7 +14479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
         <v>47</v>
       </c>
@@ -14522,7 +14523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
         <v>47</v>
       </c>
@@ -14566,7 +14567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
         <v>47</v>
       </c>
@@ -14610,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>47</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
         <v>47</v>
       </c>
@@ -14698,7 +14699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
         <v>47</v>
       </c>
@@ -14742,7 +14743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>47</v>
       </c>
@@ -14786,7 +14787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
         <v>47</v>
       </c>
@@ -14830,7 +14831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
         <v>47</v>
       </c>
@@ -14874,7 +14875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
         <v>47</v>
       </c>
@@ -14918,7 +14919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>47</v>
       </c>
@@ -14962,7 +14963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
         <v>47</v>
       </c>
@@ -15006,7 +15007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
         <v>47</v>
       </c>
@@ -15050,7 +15051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
         <v>48</v>
       </c>
@@ -15094,7 +15095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>48</v>
       </c>
@@ -15138,7 +15139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>48</v>
       </c>
@@ -15182,7 +15183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>48</v>
       </c>
@@ -15226,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>48</v>
       </c>
@@ -15270,7 +15271,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="284" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>48</v>
       </c>
@@ -15314,7 +15315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>48</v>
       </c>
@@ -15358,7 +15359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
         <v>48</v>
       </c>
@@ -15402,7 +15403,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="287" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>48</v>
       </c>
@@ -15446,7 +15447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
         <v>48</v>
       </c>
@@ -15490,7 +15491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>48</v>
       </c>
@@ -15534,7 +15535,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="290" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>48</v>
       </c>
@@ -15578,7 +15579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
         <v>49</v>
       </c>
@@ -15622,7 +15623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
         <v>49</v>
       </c>
@@ -15666,7 +15667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>49</v>
       </c>
@@ -15710,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
         <v>49</v>
       </c>
@@ -15754,7 +15755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>49</v>
       </c>
@@ -15798,7 +15799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
         <v>49</v>
       </c>
@@ -15842,7 +15843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>49</v>
       </c>
@@ -15886,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
         <v>49</v>
       </c>
@@ -15930,7 +15931,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="299" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
         <v>49</v>
       </c>
@@ -15974,7 +15975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>49</v>
       </c>
@@ -16018,7 +16019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>49</v>
       </c>
@@ -16062,7 +16063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>49</v>
       </c>
@@ -16106,7 +16107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
         <v>49</v>
       </c>
@@ -16150,7 +16151,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>49</v>
       </c>
@@ -16194,7 +16195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
         <v>50</v>
       </c>
@@ -16238,7 +16239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
         <v>50</v>
       </c>
@@ -16282,7 +16283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
         <v>50</v>
       </c>
@@ -16326,7 +16327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
         <v>50</v>
       </c>
@@ -16370,7 +16371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>50</v>
       </c>
@@ -16414,7 +16415,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="310" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
         <v>50</v>
       </c>
@@ -16458,7 +16459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>50</v>
       </c>
@@ -16502,7 +16503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
         <v>50</v>
       </c>
@@ -16546,7 +16547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
         <v>50</v>
       </c>
@@ -16590,7 +16591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>50</v>
       </c>
@@ -16634,7 +16635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
         <v>50</v>
       </c>
@@ -16678,7 +16679,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="316" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
         <v>50</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>50</v>
       </c>
@@ -16766,7 +16767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
         <v>50</v>
       </c>
@@ -16810,7 +16811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>51</v>
       </c>
@@ -16854,7 +16855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>51</v>
       </c>
@@ -16898,7 +16899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
         <v>51</v>
       </c>
@@ -16942,7 +16943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
         <v>51</v>
       </c>
@@ -16986,7 +16987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
         <v>51</v>
       </c>
@@ -17030,7 +17031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>51</v>
       </c>
@@ -17074,7 +17075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>51</v>
       </c>
@@ -17118,7 +17119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>51</v>
       </c>
@@ -17162,7 +17163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>51</v>
       </c>
@@ -17206,7 +17207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>51</v>
       </c>
@@ -17250,7 +17251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
         <v>51</v>
       </c>
@@ -17294,7 +17295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
         <v>51</v>
       </c>
@@ -17338,7 +17339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
         <v>51</v>
       </c>
@@ -17382,7 +17383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>51</v>
       </c>
@@ -17426,7 +17427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>52</v>
       </c>
@@ -17470,7 +17471,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="334" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
         <v>52</v>
       </c>
@@ -17514,7 +17515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
         <v>52</v>
       </c>
@@ -17558,7 +17559,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="336" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
         <v>52</v>
       </c>
@@ -17602,7 +17603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
         <v>52</v>
       </c>
@@ -17646,7 +17647,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="338" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
         <v>52</v>
       </c>
@@ -17690,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
         <v>52</v>
       </c>
@@ -17734,7 +17735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
         <v>52</v>
       </c>
@@ -17778,7 +17779,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="341" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
         <v>52</v>
       </c>
@@ -17822,7 +17823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>52</v>
       </c>
@@ -17866,7 +17867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>52</v>
       </c>
@@ -17910,7 +17911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
         <v>52</v>
       </c>
@@ -17954,7 +17955,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="345" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>52</v>
       </c>
@@ -17998,7 +17999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>52</v>
       </c>
@@ -18042,7 +18043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
         <v>52</v>
       </c>
@@ -18086,7 +18087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
         <v>52</v>
       </c>
@@ -18130,7 +18131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>52</v>
       </c>
@@ -18174,7 +18175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>52</v>
       </c>
@@ -18218,7 +18219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>52</v>
       </c>
@@ -18262,7 +18263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
         <v>52</v>
       </c>
@@ -18306,7 +18307,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="353" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
         <v>52</v>
       </c>
@@ -18350,7 +18351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
         <v>52</v>
       </c>
@@ -18394,7 +18395,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="355" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
         <v>52</v>
       </c>
@@ -18438,7 +18439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
         <v>52</v>
       </c>
@@ -18482,7 +18483,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="357" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>52</v>
       </c>
@@ -18526,7 +18527,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="358" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
         <v>52</v>
       </c>
@@ -18570,7 +18571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>52</v>
       </c>
@@ -18614,7 +18615,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="360" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>52</v>
       </c>
@@ -18658,7 +18659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
         <v>52</v>
       </c>
@@ -18702,7 +18703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>52</v>
       </c>
@@ -18746,7 +18747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>53</v>
       </c>
@@ -18790,7 +18791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>53</v>
       </c>
@@ -18834,7 +18835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>53</v>
       </c>
@@ -18878,7 +18879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
         <v>53</v>
       </c>
@@ -18922,7 +18923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>53</v>
       </c>
@@ -18966,7 +18967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
         <v>53</v>
       </c>
@@ -19010,7 +19011,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="369" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
         <v>53</v>
       </c>
@@ -19054,7 +19055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>53</v>
       </c>
@@ -19098,7 +19099,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="371" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
         <v>53</v>
       </c>
@@ -19142,7 +19143,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="372" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
         <v>53</v>
       </c>
@@ -19186,7 +19187,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="373" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
         <v>53</v>
       </c>
@@ -19230,7 +19231,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="374" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
         <v>53</v>
       </c>
@@ -19274,7 +19275,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="375" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>53</v>
       </c>
@@ -19318,7 +19319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>53</v>
       </c>
@@ -19362,7 +19363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>53</v>
       </c>
@@ -19406,7 +19407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>53</v>
       </c>
@@ -19450,7 +19451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
         <v>53</v>
       </c>
@@ -19494,7 +19495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
         <v>53</v>
       </c>
@@ -19538,7 +19539,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="381" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>53</v>
       </c>
@@ -19582,7 +19583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
         <v>53</v>
       </c>
@@ -19626,7 +19627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>54</v>
       </c>
@@ -19670,7 +19671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>54</v>
       </c>
@@ -19714,7 +19715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>54</v>
       </c>
@@ -19758,7 +19759,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="386" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>54</v>
       </c>
@@ -19802,7 +19803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>54</v>
       </c>
@@ -19846,7 +19847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>54</v>
       </c>
@@ -19890,7 +19891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>54</v>
       </c>
@@ -19934,7 +19935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>54</v>
       </c>
@@ -19978,7 +19979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>54</v>
       </c>
@@ -20022,7 +20023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>54</v>
       </c>
@@ -20066,7 +20067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
         <v>54</v>
       </c>
@@ -20110,7 +20111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>54</v>
       </c>
@@ -20154,7 +20155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>54</v>
       </c>
@@ -20198,7 +20199,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="396" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>54</v>
       </c>
@@ -20242,7 +20243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>54</v>
       </c>
@@ -20286,7 +20287,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="398" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>54</v>
       </c>
@@ -20330,7 +20331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>54</v>
       </c>
@@ -20374,7 +20375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>54</v>
       </c>
@@ -20418,7 +20419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>54</v>
       </c>
@@ -20462,7 +20463,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="402" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>54</v>
       </c>
@@ -20506,7 +20507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
         <v>54</v>
       </c>
@@ -20550,7 +20551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>54</v>
       </c>
@@ -20594,7 +20595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
         <v>54</v>
       </c>
@@ -20638,7 +20639,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="406" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>54</v>
       </c>
@@ -20682,7 +20683,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="407" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
         <v>54</v>
       </c>
@@ -20726,7 +20727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
         <v>55</v>
       </c>
@@ -20770,7 +20771,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="409" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
         <v>55</v>
       </c>
@@ -20814,7 +20815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
         <v>55</v>
       </c>
@@ -20858,7 +20859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
         <v>55</v>
       </c>
@@ -20902,7 +20903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
         <v>55</v>
       </c>
@@ -20946,7 +20947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>55</v>
       </c>
@@ -20990,7 +20991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>55</v>
       </c>
@@ -21034,7 +21035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>55</v>
       </c>
@@ -21078,7 +21079,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="416" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
         <v>55</v>
       </c>
@@ -21122,7 +21123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
         <v>56</v>
       </c>
@@ -21166,7 +21167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
         <v>56</v>
       </c>
@@ -21210,7 +21211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>56</v>
       </c>
@@ -21254,7 +21255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>56</v>
       </c>
@@ -21298,7 +21299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
         <v>56</v>
       </c>
@@ -21342,7 +21343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
         <v>56</v>
       </c>
@@ -21386,7 +21387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
         <v>56</v>
       </c>
@@ -21430,7 +21431,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="424" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
         <v>56</v>
       </c>
@@ -21474,7 +21475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
         <v>56</v>
       </c>
@@ -21518,7 +21519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
         <v>56</v>
       </c>
@@ -21562,7 +21563,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="427" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>56</v>
       </c>
@@ -21606,7 +21607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
         <v>56</v>
       </c>
@@ -21650,7 +21651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>57</v>
       </c>
@@ -21694,7 +21695,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="430" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
         <v>57</v>
       </c>
@@ -21738,7 +21739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
         <v>57</v>
       </c>
@@ -21782,7 +21783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
         <v>57</v>
       </c>
@@ -21826,7 +21827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
         <v>57</v>
       </c>
@@ -21870,7 +21871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>57</v>
       </c>
@@ -21914,7 +21915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
         <v>57</v>
       </c>
@@ -21958,7 +21959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>57</v>
       </c>
@@ -22002,7 +22003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
         <v>57</v>
       </c>
@@ -22046,7 +22047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
         <v>57</v>
       </c>
@@ -22090,7 +22091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
         <v>57</v>
       </c>
@@ -22134,7 +22135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
         <v>57</v>
       </c>
@@ -22178,7 +22179,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="441" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
         <v>57</v>
       </c>
@@ -22222,7 +22223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
         <v>57</v>
       </c>
@@ -22266,7 +22267,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="443" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
         <v>57</v>
       </c>
@@ -22310,7 +22311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
         <v>57</v>
       </c>
@@ -22354,7 +22355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
         <v>57</v>
       </c>
@@ -22398,7 +22399,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="446" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
         <v>57</v>
       </c>
@@ -22442,7 +22443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
         <v>57</v>
       </c>
@@ -22486,7 +22487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
         <v>58</v>
       </c>
@@ -22530,7 +22531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
         <v>58</v>
       </c>
@@ -22574,7 +22575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
         <v>58</v>
       </c>
@@ -22618,7 +22619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
         <v>58</v>
       </c>
@@ -22662,7 +22663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
         <v>58</v>
       </c>
@@ -22706,7 +22707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
         <v>58</v>
       </c>
@@ -22750,7 +22751,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="454" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
         <v>58</v>
       </c>
@@ -22794,7 +22795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>58</v>
       </c>
@@ -22838,7 +22839,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="456" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
         <v>58</v>
       </c>
@@ -22882,7 +22883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
         <v>58</v>
       </c>
@@ -22926,7 +22927,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="458" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
         <v>58</v>
       </c>
@@ -22970,7 +22971,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="459" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
         <v>58</v>
       </c>
@@ -23014,7 +23015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
         <v>58</v>
       </c>
@@ -23058,7 +23059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
         <v>58</v>
       </c>
@@ -23102,7 +23103,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="462" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
         <v>58</v>
       </c>
@@ -23146,7 +23147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
         <v>58</v>
       </c>
@@ -23190,7 +23191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
         <v>58</v>
       </c>
@@ -23234,7 +23235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
         <v>58</v>
       </c>
@@ -23278,7 +23279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
         <v>58</v>
       </c>
@@ -23322,7 +23323,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="467" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
         <v>58</v>
       </c>
@@ -23366,7 +23367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
         <v>58</v>
       </c>
@@ -23410,7 +23411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
         <v>58</v>
       </c>
@@ -23454,7 +23455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
         <v>59</v>
       </c>
@@ -23498,7 +23499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
         <v>59</v>
       </c>
@@ -23542,7 +23543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
         <v>59</v>
       </c>
@@ -23586,7 +23587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
         <v>59</v>
       </c>
@@ -23630,7 +23631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
         <v>59</v>
       </c>
@@ -23674,7 +23675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>59</v>
       </c>
@@ -23718,7 +23719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
         <v>59</v>
       </c>
@@ -23762,7 +23763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
         <v>59</v>
       </c>
@@ -23806,7 +23807,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="478" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
         <v>59</v>
       </c>
@@ -23850,7 +23851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
         <v>59</v>
       </c>
@@ -23894,7 +23895,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="480" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
         <v>59</v>
       </c>
@@ -23938,7 +23939,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="481" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
         <v>59</v>
       </c>
@@ -23982,7 +23983,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="482" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
         <v>59</v>
       </c>
@@ -24026,7 +24027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
         <v>59</v>
       </c>
@@ -24070,7 +24071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
         <v>59</v>
       </c>
@@ -24114,7 +24115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
         <v>59</v>
       </c>
@@ -24158,7 +24159,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="486" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
         <v>59</v>
       </c>
@@ -24202,7 +24203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
         <v>59</v>
       </c>
@@ -24246,7 +24247,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="488" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
         <v>59</v>
       </c>
@@ -24290,7 +24291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
         <v>59</v>
       </c>
@@ -24334,7 +24335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
         <v>59</v>
       </c>
@@ -24378,7 +24379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
         <v>59</v>
       </c>
@@ -24422,7 +24423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
         <v>59</v>
       </c>
@@ -24466,7 +24467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
         <v>59</v>
       </c>
@@ -24510,7 +24511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
         <v>60</v>
       </c>
@@ -24554,7 +24555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
         <v>60</v>
       </c>
@@ -24598,7 +24599,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="496" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
         <v>60</v>
       </c>
@@ -24642,7 +24643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
         <v>60</v>
       </c>
@@ -24686,7 +24687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
         <v>60</v>
       </c>
@@ -24730,7 +24731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
         <v>60</v>
       </c>
@@ -24774,7 +24775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
         <v>60</v>
       </c>
@@ -24818,7 +24819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
         <v>60</v>
       </c>
@@ -24862,7 +24863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
         <v>60</v>
       </c>
@@ -24906,7 +24907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
         <v>60</v>
       </c>
@@ -24950,7 +24951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
         <v>60</v>
       </c>
@@ -24994,7 +24995,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="505" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
         <v>60</v>
       </c>
@@ -25038,7 +25039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
         <v>60</v>
       </c>
@@ -25082,7 +25083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
         <v>60</v>
       </c>
@@ -25126,7 +25127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
         <v>60</v>
       </c>
@@ -25170,7 +25171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
         <v>60</v>
       </c>
@@ -25214,7 +25215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
         <v>60</v>
       </c>
@@ -25258,7 +25259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
         <v>60</v>
       </c>
@@ -25302,7 +25303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
         <v>61</v>
       </c>
@@ -25346,7 +25347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
         <v>61</v>
       </c>
@@ -25390,7 +25391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
         <v>61</v>
       </c>
@@ -25434,7 +25435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
         <v>61</v>
       </c>
@@ -25478,7 +25479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
         <v>61</v>
       </c>
@@ -25522,7 +25523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
         <v>61</v>
       </c>
@@ -25566,7 +25567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
         <v>61</v>
       </c>
@@ -25610,7 +25611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
         <v>61</v>
       </c>
@@ -25654,7 +25655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
         <v>61</v>
       </c>
@@ -25698,7 +25699,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="521" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
         <v>61</v>
       </c>
@@ -25742,7 +25743,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="522" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
         <v>61</v>
       </c>
@@ -25786,7 +25787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
         <v>61</v>
       </c>
@@ -25830,7 +25831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
         <v>61</v>
       </c>
@@ -25874,7 +25875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
         <v>61</v>
       </c>
@@ -25918,7 +25919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
         <v>61</v>
       </c>
@@ -25962,7 +25963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
         <v>62</v>
       </c>
@@ -26006,7 +26007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="s">
         <v>62</v>
       </c>
@@ -26050,7 +26051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
         <v>62</v>
       </c>
@@ -26094,7 +26095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
         <v>62</v>
       </c>
@@ -26138,7 +26139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>62</v>
       </c>
@@ -26182,7 +26183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
         <v>62</v>
       </c>
@@ -26226,7 +26227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
         <v>62</v>
       </c>
@@ -26270,7 +26271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
         <v>62</v>
       </c>
@@ -26314,7 +26315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>62</v>
       </c>
@@ -26358,7 +26359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
         <v>62</v>
       </c>
@@ -26402,7 +26403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
         <v>62</v>
       </c>
@@ -26446,7 +26447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
         <v>62</v>
       </c>
@@ -26490,7 +26491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
         <v>62</v>
       </c>
@@ -26534,7 +26535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="s">
         <v>62</v>
       </c>
@@ -26578,7 +26579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="s">
         <v>62</v>
       </c>
@@ -26622,7 +26623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="s">
         <v>62</v>
       </c>
@@ -26666,7 +26667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="s">
         <v>62</v>
       </c>
@@ -26710,7 +26711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="s">
         <v>62</v>
       </c>
@@ -26754,7 +26755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="s">
         <v>62</v>
       </c>
@@ -26798,7 +26799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A546" s="1" t="s">
         <v>62</v>
       </c>
@@ -26842,7 +26843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="s">
         <v>62</v>
       </c>
@@ -26886,7 +26887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="s">
         <v>62</v>
       </c>
@@ -26930,7 +26931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>62</v>
       </c>
@@ -26974,7 +26975,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="550" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
         <v>62</v>
       </c>
@@ -27018,7 +27019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A551" s="1" t="s">
         <v>62</v>
       </c>
@@ -27062,7 +27063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="s">
         <v>62</v>
       </c>
@@ -27106,7 +27107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="s">
         <v>62</v>
       </c>
@@ -27150,7 +27151,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="554" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A554" s="1" t="s">
         <v>62</v>
       </c>
@@ -27194,7 +27195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A555" s="1" t="s">
         <v>62</v>
       </c>
@@ -27238,7 +27239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A556" s="1" t="s">
         <v>62</v>
       </c>
@@ -27282,7 +27283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A557" s="1" t="s">
         <v>62</v>
       </c>
@@ -27326,7 +27327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A558" s="1" t="s">
         <v>62</v>
       </c>
@@ -27370,7 +27371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A559" s="1" t="s">
         <v>62</v>
       </c>
@@ -27414,7 +27415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A560" s="1" t="s">
         <v>62</v>
       </c>
@@ -27458,7 +27459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A561" s="1" t="s">
         <v>62</v>
       </c>
@@ -27502,7 +27503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A562" s="1" t="s">
         <v>62</v>
       </c>
@@ -27546,7 +27547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="s">
         <v>62</v>
       </c>
@@ -27590,7 +27591,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="564" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="s">
         <v>62</v>
       </c>
@@ -27634,7 +27635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A565" s="1" t="s">
         <v>62</v>
       </c>
@@ -27678,7 +27679,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="566" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A566" s="1" t="s">
         <v>62</v>
       </c>
@@ -27722,7 +27723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A567" s="1" t="s">
         <v>63</v>
       </c>
@@ -27766,7 +27767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A568" s="1" t="s">
         <v>63</v>
       </c>
@@ -27810,7 +27811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A569" s="1" t="s">
         <v>63</v>
       </c>
@@ -27854,7 +27855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A570" s="1" t="s">
         <v>63</v>
       </c>
@@ -27898,7 +27899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A571" s="1" t="s">
         <v>63</v>
       </c>
@@ -27942,7 +27943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A572" s="1" t="s">
         <v>63</v>
       </c>
@@ -27986,7 +27987,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="573" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A573" s="1" t="s">
         <v>63</v>
       </c>
@@ -28030,7 +28031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A574" s="1" t="s">
         <v>63</v>
       </c>
@@ -28074,7 +28075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="s">
         <v>63</v>
       </c>
@@ -28118,7 +28119,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="576" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A576" s="1" t="s">
         <v>63</v>
       </c>
@@ -28162,7 +28163,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="577" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A577" s="1" t="s">
         <v>63</v>
       </c>
@@ -28206,7 +28207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A578" s="1" t="s">
         <v>63</v>
       </c>
@@ -28250,7 +28251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A579" s="1" t="s">
         <v>64</v>
       </c>
@@ -28294,7 +28295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A580" s="1" t="s">
         <v>64</v>
       </c>
@@ -28338,7 +28339,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="581" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A581" s="1" t="s">
         <v>64</v>
       </c>
@@ -28382,7 +28383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A582" s="1" t="s">
         <v>64</v>
       </c>
@@ -28426,7 +28427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A583" s="1" t="s">
         <v>64</v>
       </c>
@@ -28470,7 +28471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A584" s="1" t="s">
         <v>64</v>
       </c>
@@ -28514,7 +28515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A585" s="1" t="s">
         <v>64</v>
       </c>
@@ -28558,7 +28559,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="586" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A586" s="1" t="s">
         <v>64</v>
       </c>
@@ -28602,7 +28603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A587" s="1" t="s">
         <v>64</v>
       </c>
@@ -28646,7 +28647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A588" s="1" t="s">
         <v>64</v>
       </c>
@@ -28690,7 +28691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A589" s="1" t="s">
         <v>64</v>
       </c>
@@ -28734,7 +28735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A590" s="1" t="s">
         <v>64</v>
       </c>
@@ -28778,7 +28779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A591" s="1" t="s">
         <v>64</v>
       </c>
@@ -28822,7 +28823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A592" s="1" t="s">
         <v>64</v>
       </c>
@@ -28866,7 +28867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A593" s="1" t="s">
         <v>64</v>
       </c>
@@ -28910,7 +28911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A594" s="1" t="s">
         <v>64</v>
       </c>
@@ -28954,7 +28955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A595" s="1" t="s">
         <v>64</v>
       </c>
@@ -28998,7 +28999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A596" s="1" t="s">
         <v>64</v>
       </c>
@@ -29042,7 +29043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A597" s="1" t="s">
         <v>64</v>
       </c>
@@ -29086,7 +29087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A598" s="1" t="s">
         <v>64</v>
       </c>
@@ -29130,7 +29131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A599" s="1" t="s">
         <v>65</v>
       </c>
@@ -29174,7 +29175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A600" s="1" t="s">
         <v>65</v>
       </c>
@@ -29218,7 +29219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A601" s="1" t="s">
         <v>65</v>
       </c>
@@ -29262,7 +29263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A602" s="1" t="s">
         <v>65</v>
       </c>
@@ -29306,7 +29307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A603" s="1" t="s">
         <v>65</v>
       </c>
@@ -29350,7 +29351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A604" s="1" t="s">
         <v>65</v>
       </c>
@@ -29394,7 +29395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A605" s="1" t="s">
         <v>65</v>
       </c>
@@ -29438,7 +29439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A606" s="1" t="s">
         <v>65</v>
       </c>
@@ -29482,7 +29483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A607" s="1" t="s">
         <v>65</v>
       </c>
@@ -29526,7 +29527,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="608" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A608" s="1" t="s">
         <v>65</v>
       </c>
@@ -29570,7 +29571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A609" s="1" t="s">
         <v>65</v>
       </c>
@@ -29614,7 +29615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A610" s="1" t="s">
         <v>65</v>
       </c>
@@ -29658,7 +29659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A611" s="1" t="s">
         <v>65</v>
       </c>
@@ -29702,7 +29703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A612" s="1" t="s">
         <v>65</v>
       </c>
@@ -29746,7 +29747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A613" s="1" t="s">
         <v>65</v>
       </c>
@@ -29790,7 +29791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A614" s="1" t="s">
         <v>65</v>
       </c>
@@ -29834,7 +29835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A615" s="1" t="s">
         <v>65</v>
       </c>
@@ -29878,7 +29879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A616" s="1" t="s">
         <v>65</v>
       </c>
@@ -29922,7 +29923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A617" s="1" t="s">
         <v>65</v>
       </c>
@@ -29966,7 +29967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A618" s="1" t="s">
         <v>65</v>
       </c>
@@ -30010,7 +30011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A619" s="1" t="s">
         <v>66</v>
       </c>
@@ -30054,7 +30055,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="620" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A620" s="1" t="s">
         <v>66</v>
       </c>
@@ -30098,7 +30099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A621" s="1" t="s">
         <v>66</v>
       </c>
@@ -30142,7 +30143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A622" s="1" t="s">
         <v>66</v>
       </c>
@@ -30186,7 +30187,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="623" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A623" s="1" t="s">
         <v>66</v>
       </c>
@@ -30230,7 +30231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A624" s="1" t="s">
         <v>66</v>
       </c>
@@ -30274,7 +30275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A625" s="1" t="s">
         <v>66</v>
       </c>
@@ -30318,7 +30319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A626" s="1" t="s">
         <v>66</v>
       </c>
@@ -30362,7 +30363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A627" s="1" t="s">
         <v>66</v>
       </c>
@@ -30406,7 +30407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A628" s="1" t="s">
         <v>66</v>
       </c>
@@ -30450,7 +30451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A629" s="1" t="s">
         <v>66</v>
       </c>
@@ -30494,7 +30495,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="630" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A630" s="1" t="s">
         <v>66</v>
       </c>
@@ -30538,7 +30539,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="631" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A631" s="1" t="s">
         <v>66</v>
       </c>
@@ -30582,7 +30583,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="632" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A632" s="1" t="s">
         <v>66</v>
       </c>
@@ -30626,7 +30627,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="633" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A633" s="1" t="s">
         <v>66</v>
       </c>
@@ -30670,7 +30671,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="634" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A634" s="1" t="s">
         <v>66</v>
       </c>
@@ -30714,7 +30715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A635" s="1" t="s">
         <v>66</v>
       </c>
@@ -30758,7 +30759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A636" s="1" t="s">
         <v>66</v>
       </c>
@@ -30802,7 +30803,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="637" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A637" s="1" t="s">
         <v>66</v>
       </c>
@@ -30846,7 +30847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A638" s="1" t="s">
         <v>66</v>
       </c>
@@ -30890,7 +30891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A639" s="1" t="s">
         <v>66</v>
       </c>
@@ -30934,7 +30935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A640" s="1" t="s">
         <v>66</v>
       </c>
@@ -30978,7 +30979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A641" s="1" t="s">
         <v>66</v>
       </c>
@@ -31022,7 +31023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A642" s="1" t="s">
         <v>66</v>
       </c>
@@ -31066,7 +31067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A643" s="1" t="s">
         <v>66</v>
       </c>
@@ -31110,7 +31111,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="644" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A644" s="1" t="s">
         <v>67</v>
       </c>
@@ -31154,7 +31155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A645" s="1" t="s">
         <v>67</v>
       </c>
@@ -31198,7 +31199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A646" s="1" t="s">
         <v>67</v>
       </c>
@@ -31242,7 +31243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A647" s="1" t="s">
         <v>67</v>
       </c>
@@ -31286,7 +31287,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="648" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A648" s="1" t="s">
         <v>67</v>
       </c>
@@ -31330,7 +31331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A649" s="1" t="s">
         <v>67</v>
       </c>
@@ -31374,7 +31375,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="650" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A650" s="1" t="s">
         <v>67</v>
       </c>
@@ -31418,7 +31419,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="651" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A651" s="1" t="s">
         <v>67</v>
       </c>
@@ -31462,7 +31463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A652" s="1" t="s">
         <v>67</v>
       </c>
@@ -31506,7 +31507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A653" s="1" t="s">
         <v>67</v>
       </c>
@@ -31550,7 +31551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A654" s="1" t="s">
         <v>67</v>
       </c>
@@ -31594,7 +31595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A655" s="1" t="s">
         <v>67</v>
       </c>
@@ -31638,7 +31639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A656" s="1" t="s">
         <v>67</v>
       </c>
@@ -31682,7 +31683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A657" s="1" t="s">
         <v>67</v>
       </c>
@@ -31726,7 +31727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="s">
         <v>67</v>
       </c>
@@ -31770,7 +31771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A659" s="1" t="s">
         <v>67</v>
       </c>
@@ -31814,7 +31815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A660" s="1" t="s">
         <v>67</v>
       </c>
@@ -31858,7 +31859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A661" s="1" t="s">
         <v>67</v>
       </c>
@@ -31902,7 +31903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A662" s="1" t="s">
         <v>67</v>
       </c>
@@ -31946,7 +31947,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="663" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A663" s="1" t="s">
         <v>67</v>
       </c>
@@ -31990,7 +31991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A664" s="1" t="s">
         <v>67</v>
       </c>
@@ -32034,7 +32035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A665" s="1" t="s">
         <v>67</v>
       </c>
@@ -32078,7 +32079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A666" s="1" t="s">
         <v>68</v>
       </c>
@@ -32122,7 +32123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A667" s="1" t="s">
         <v>68</v>
       </c>
@@ -32166,7 +32167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A668" s="1" t="s">
         <v>68</v>
       </c>
@@ -32210,7 +32211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A669" s="1" t="s">
         <v>68</v>
       </c>
@@ -32254,7 +32255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A670" s="1" t="s">
         <v>68</v>
       </c>
@@ -32298,7 +32299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A671" s="1" t="s">
         <v>68</v>
       </c>
@@ -32342,7 +32343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A672" s="1" t="s">
         <v>68</v>
       </c>
@@ -32386,7 +32387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A673" s="1" t="s">
         <v>68</v>
       </c>
@@ -32430,7 +32431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A674" s="1" t="s">
         <v>68</v>
       </c>
@@ -32474,7 +32475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A675" s="1" t="s">
         <v>68</v>
       </c>
@@ -32518,7 +32519,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="676" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A676" s="1" t="s">
         <v>68</v>
       </c>
@@ -32562,7 +32563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A677" s="1" t="s">
         <v>68</v>
       </c>
@@ -32606,7 +32607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A678" s="1" t="s">
         <v>68</v>
       </c>
@@ -32650,7 +32651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A679" s="1" t="s">
         <v>68</v>
       </c>
@@ -32694,7 +32695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A680" s="1" t="s">
         <v>68</v>
       </c>
@@ -32738,7 +32739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A681" s="1" t="s">
         <v>68</v>
       </c>
@@ -32782,7 +32783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A682" s="1" t="s">
         <v>69</v>
       </c>
@@ -32826,7 +32827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A683" s="1" t="s">
         <v>69</v>
       </c>
@@ -32870,7 +32871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A684" s="1" t="s">
         <v>69</v>
       </c>
@@ -32914,7 +32915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A685" s="1" t="s">
         <v>69</v>
       </c>
@@ -32958,7 +32959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A686" s="1" t="s">
         <v>69</v>
       </c>
@@ -33002,7 +33003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A687" s="1" t="s">
         <v>69</v>
       </c>
@@ -33046,7 +33047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A688" s="1" t="s">
         <v>69</v>
       </c>
@@ -33090,7 +33091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A689" s="1" t="s">
         <v>69</v>
       </c>
@@ -33134,7 +33135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A690" s="1" t="s">
         <v>69</v>
       </c>
@@ -33178,7 +33179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A691" s="1" t="s">
         <v>69</v>
       </c>
@@ -33222,7 +33223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A692" s="1" t="s">
         <v>69</v>
       </c>
@@ -33266,7 +33267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A693" s="1" t="s">
         <v>69</v>
       </c>
@@ -33310,7 +33311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A694" s="1" t="s">
         <v>70</v>
       </c>
@@ -33354,7 +33355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A695" s="1" t="s">
         <v>70</v>
       </c>
@@ -33398,7 +33399,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="696" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A696" s="1" t="s">
         <v>70</v>
       </c>
@@ -33442,7 +33443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A697" s="1" t="s">
         <v>70</v>
       </c>
@@ -33486,7 +33487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A698" s="1" t="s">
         <v>70</v>
       </c>
@@ -33530,7 +33531,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="699" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A699" s="1" t="s">
         <v>70</v>
       </c>
@@ -33574,7 +33575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A700" s="1" t="s">
         <v>70</v>
       </c>
@@ -33618,7 +33619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A701" s="1" t="s">
         <v>70</v>
       </c>
@@ -33662,7 +33663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A702" s="1" t="s">
         <v>70</v>
       </c>
@@ -33706,7 +33707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A703" s="1" t="s">
         <v>70</v>
       </c>
@@ -33750,7 +33751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A704" s="1" t="s">
         <v>70</v>
       </c>
@@ -33794,7 +33795,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="705" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A705" s="1" t="s">
         <v>70</v>
       </c>
@@ -33838,7 +33839,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="706" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A706" s="1" t="s">
         <v>70</v>
       </c>
@@ -33882,7 +33883,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="707" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A707" s="1" t="s">
         <v>70</v>
       </c>
@@ -33926,7 +33927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A708" s="1" t="s">
         <v>70</v>
       </c>
@@ -33970,7 +33971,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="709" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A709" s="1" t="s">
         <v>70</v>
       </c>
@@ -34014,7 +34015,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="710" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A710" s="1" t="s">
         <v>70</v>
       </c>
@@ -34058,7 +34059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A711" s="1" t="s">
         <v>70</v>
       </c>
@@ -34102,7 +34103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A712" s="1" t="s">
         <v>70</v>
       </c>
@@ -34146,7 +34147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A713" s="1" t="s">
         <v>70</v>
       </c>
@@ -34190,7 +34191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A714" s="1" t="s">
         <v>70</v>
       </c>
@@ -34234,7 +34235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A715" s="1" t="s">
         <v>70</v>
       </c>
@@ -34278,7 +34279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A716" s="1" t="s">
         <v>70</v>
       </c>
@@ -34322,7 +34323,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="717" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A717" s="1" t="s">
         <v>70</v>
       </c>
@@ -34366,7 +34367,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="718" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A718" s="1" t="s">
         <v>70</v>
       </c>
@@ -34410,7 +34411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A719" s="1" t="s">
         <v>71</v>
       </c>
@@ -34454,7 +34455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="720" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A720" s="1" t="s">
         <v>71</v>
       </c>
@@ -34498,7 +34499,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="721" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A721" s="1" t="s">
         <v>71</v>
       </c>
@@ -34542,7 +34543,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="722" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A722" s="1" t="s">
         <v>71</v>
       </c>
@@ -34586,7 +34587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A723" s="1" t="s">
         <v>71</v>
       </c>
@@ -34630,7 +34631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A724" s="1" t="s">
         <v>71</v>
       </c>
@@ -34674,7 +34675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A725" s="1" t="s">
         <v>71</v>
       </c>
@@ -34718,7 +34719,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="726" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A726" s="1" t="s">
         <v>71</v>
       </c>
@@ -34762,7 +34763,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="727" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A727" s="1" t="s">
         <v>71</v>
       </c>
@@ -34806,7 +34807,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="728" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A728" s="1" t="s">
         <v>71</v>
       </c>
@@ -34850,7 +34851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A729" s="1" t="s">
         <v>71</v>
       </c>
@@ -34894,7 +34895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A730" s="1" t="s">
         <v>71</v>
       </c>
@@ -34938,7 +34939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A731" s="1" t="s">
         <v>71</v>
       </c>
@@ -34982,7 +34983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="732" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A732" s="1" t="s">
         <v>71</v>
       </c>
@@ -35026,7 +35027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A733" s="1" t="s">
         <v>71</v>
       </c>
@@ -35070,7 +35071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A734" s="1" t="s">
         <v>71</v>
       </c>
@@ -35114,7 +35115,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="735" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A735" s="1" t="s">
         <v>71</v>
       </c>
@@ -35158,7 +35159,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="736" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A736" s="1" t="s">
         <v>71</v>
       </c>
@@ -35203,7 +35204,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="1.25" right="1.25" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35213,38 +35214,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Y42"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -35321,7 +35322,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -35398,7 +35399,7 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -35475,7 +35476,7 @@
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -35552,7 +35553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -35629,7 +35630,7 @@
         <v>0.14204545454545456</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -35706,7 +35707,7 @@
         <v>0.36538461538461536</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -35783,7 +35784,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -35860,7 +35861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -35937,7 +35938,7 @@
         <v>9.375E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -36014,7 +36015,7 @@
         <v>0.109375</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -36091,7 +36092,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -36168,7 +36169,7 @@
         <v>0.140625</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -36245,7 +36246,7 @@
         <v>0.10416666666666667</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -36322,7 +36323,7 @@
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -36399,7 +36400,7 @@
         <v>3.8461538461538464E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -36476,7 +36477,7 @@
         <v>0.11413043478260869</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -36553,7 +36554,7 @@
         <v>0.15384615384615385</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -36630,7 +36631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -36707,7 +36708,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -36784,7 +36785,7 @@
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -36861,7 +36862,7 @@
         <v>0.3392857142857143</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -36938,7 +36939,7 @@
         <v>0.35714285714285715</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -37015,7 +37016,7 @@
         <v>0.20833333333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -37092,7 +37093,7 @@
         <v>0.28749999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -37169,7 +37170,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -37246,7 +37247,7 @@
         <v>0.30555555555555558</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -37323,7 +37324,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -37400,7 +37401,7 @@
         <v>9.2105263157894732E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -37477,7 +37478,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -37554,7 +37555,7 @@
         <v>0.27083333333333331</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -37631,7 +37632,7 @@
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -37708,7 +37709,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -37785,7 +37786,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -37862,7 +37863,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>64</v>
       </c>
@@ -37939,7 +37940,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>65</v>
       </c>
@@ -38016,7 +38017,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -38093,7 +38094,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -38170,7 +38171,7 @@
         <v>0.13636363636363635</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -38247,7 +38248,7 @@
         <v>4.6875E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -38324,7 +38325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>70</v>
       </c>
@@ -38401,7 +38402,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>71</v>
       </c>
